--- a/avg_power_consumption.xlsx
+++ b/avg_power_consumption.xlsx
@@ -1,18 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\91829\Downloads\New folder\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{348E9A70-CDA2-46A3-86BD-A777F8F99E78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Sheet1" sheetId="1" r:id="rId4"/>
-    <sheet state="visible" name="Sheet2" sheetId="2" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="37">
   <si>
     <t>Benchmark</t>
   </si>
@@ -41,9 +50,6 @@
     <t>Power draw(W)</t>
   </si>
   <si>
-    <t>Temperature</t>
-  </si>
-  <si>
     <t>Matrix_Multiplication</t>
   </si>
   <si>
@@ -56,6 +62,9 @@
     <t>1*1</t>
   </si>
   <si>
+    <t>-----</t>
+  </si>
+  <si>
     <t>2048*2048</t>
   </si>
   <si>
@@ -92,31 +101,7 @@
     <t>-------</t>
   </si>
   <si>
-    <t>-----</t>
-  </si>
-  <si>
     <t>------</t>
-  </si>
-  <si>
-    <t>Kernel Name</t>
-  </si>
-  <si>
-    <t>Block Size</t>
-  </si>
-  <si>
-    <t>Total Threads per Block</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Loop Unrolling </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shared Memory </t>
-  </si>
-  <si>
-    <t>Execution Time (ms)</t>
-  </si>
-  <si>
-    <t>Power Consumed (W)</t>
   </si>
   <si>
     <t>Matrix_Transpose</t>
@@ -152,20 +137,22 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
-      <sz val="10.0"/>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
     </font>
@@ -175,68 +162,60 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
-    <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="3" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
     <dxf>
-      <font/>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFB7E1CD"/>
           <bgColor rgb="FFB7E1CD"/>
         </patternFill>
       </fill>
-      <border/>
     </dxf>
   </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -426,27 +405,30 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:I112"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="15.5"/>
-    <col customWidth="1" min="2" max="2" width="18.38"/>
-    <col customWidth="1" min="5" max="5" width="18.75"/>
-    <col customWidth="1" min="6" max="6" width="14.5"/>
-    <col customWidth="1" min="7" max="7" width="17.5"/>
-    <col customWidth="1" min="8" max="8" width="20.25"/>
-    <col customWidth="1" min="9" max="9" width="17.88"/>
+    <col min="1" max="1" width="15.42578125" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" customWidth="1"/>
+    <col min="7" max="7" width="17.42578125" customWidth="1"/>
+    <col min="8" max="8" width="20.28515625" customWidth="1"/>
+    <col min="9" max="9" width="17.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -474,43 +456,37 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="3">
+        <v>16777216</v>
+      </c>
+      <c r="F2" s="1">
+        <v>1</v>
+      </c>
+      <c r="G2" s="1">
+        <v>8</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="3">
-        <v>1.6777216E7</v>
-      </c>
-      <c r="F2" s="1">
-        <v>1.0</v>
-      </c>
-      <c r="G2" s="1">
-        <v>8.0</v>
-      </c>
-      <c r="H2" s="1">
-        <v>4417.139</v>
-      </c>
-      <c r="I2" s="4">
-        <v>21.63600000000001</v>
-      </c>
-      <c r="J2" s="5">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="I2" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C3" s="1" t="s">
         <v>14</v>
       </c>
@@ -518,25 +494,22 @@
         <v>15</v>
       </c>
       <c r="E3" s="3">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F3" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G3" s="1">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="H3" s="1">
-        <v>667.859</v>
+        <v>667.721</v>
       </c>
       <c r="I3" s="1">
-        <v>21.706</v>
-      </c>
-      <c r="J3" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>245.37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C4" s="1" t="s">
         <v>16</v>
       </c>
@@ -544,25 +517,22 @@
         <v>17</v>
       </c>
       <c r="E4" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F4" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
-        <v>128.0</v>
+        <v>128</v>
       </c>
       <c r="H4" s="1">
-        <v>115.38</v>
+        <v>116.476</v>
       </c>
       <c r="I4" s="1">
-        <v>21.877999999999982</v>
-      </c>
-      <c r="J4" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>196.05</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
         <v>18</v>
       </c>
@@ -570,25 +540,22 @@
         <v>19</v>
       </c>
       <c r="E5" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F5" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G5" s="1">
-        <v>512.0</v>
+        <v>512</v>
       </c>
       <c r="H5" s="1">
-        <v>36.282</v>
+        <v>36.692</v>
       </c>
       <c r="I5" s="1">
-        <v>21.723999999999993</v>
-      </c>
-      <c r="J5" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>73.349999999999994</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C6" s="1" t="s">
         <v>20</v>
       </c>
@@ -596,25 +563,22 @@
         <v>21</v>
       </c>
       <c r="E6" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F6" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>2048.0</v>
+        <v>2048</v>
       </c>
       <c r="H6" s="1">
-        <v>25.964</v>
+        <v>26.155999999999999</v>
       </c>
       <c r="I6" s="1">
-        <v>22.071666666666665</v>
-      </c>
-      <c r="J6" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>56.44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>22</v>
       </c>
@@ -622,39 +586,36 @@
         <v>23</v>
       </c>
       <c r="E7" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F7" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>8192.0</v>
+        <v>8192</v>
       </c>
       <c r="H7" s="1">
-        <v>26.029</v>
+        <v>26.11</v>
       </c>
       <c r="I7" s="1">
-        <v>21.940999999999995</v>
-      </c>
-      <c r="J7" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>54.21</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E10" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F10" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G10" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>24</v>
@@ -662,11 +623,8 @@
       <c r="I10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11">
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>14</v>
       </c>
@@ -674,25 +632,22 @@
         <v>15</v>
       </c>
       <c r="E11" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F11" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G11" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H11" s="1">
-        <v>288.935</v>
-      </c>
-      <c r="I11" s="4">
-        <v>249.66000000000003</v>
-      </c>
-      <c r="J11" s="4">
-        <v>74.31111111111112</v>
-      </c>
-    </row>
-    <row r="12">
+        <v>294.41500000000002</v>
+      </c>
+      <c r="I11" s="1">
+        <v>249.71</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>16</v>
       </c>
@@ -700,25 +655,22 @@
         <v>17</v>
       </c>
       <c r="E12" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F12" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>92.982</v>
-      </c>
-      <c r="I12" s="4">
-        <v>152.3766666666666</v>
-      </c>
-      <c r="J12" s="4">
-        <v>62.333333333333336</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>95.087000000000003</v>
+      </c>
+      <c r="I12" s="1">
+        <v>163.79</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>18</v>
       </c>
@@ -726,25 +678,22 @@
         <v>19</v>
       </c>
       <c r="E13" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F13" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H13" s="1">
-        <v>46.412</v>
-      </c>
-      <c r="I13" s="4">
-        <v>58.269555555555534</v>
-      </c>
-      <c r="J13" s="4">
-        <v>54.266666666666666</v>
-      </c>
-    </row>
-    <row r="14">
+        <v>47.192</v>
+      </c>
+      <c r="I13" s="1">
+        <v>99.22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>20</v>
       </c>
@@ -752,25 +701,22 @@
         <v>21</v>
       </c>
       <c r="E14" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F14" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G14" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H14" s="1">
-        <v>37.235</v>
-      </c>
-      <c r="I14" s="4">
-        <v>77.60377777777775</v>
-      </c>
-      <c r="J14" s="4">
-        <v>52.77777777777778</v>
-      </c>
-    </row>
-    <row r="15">
+        <v>37.795000000000002</v>
+      </c>
+      <c r="I14" s="1">
+        <v>80.3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>22</v>
       </c>
@@ -778,39 +724,36 @@
         <v>23</v>
       </c>
       <c r="E15" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F15" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G15" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H15" s="1">
-        <v>35.336</v>
-      </c>
-      <c r="I15" s="4">
-        <v>70.65355555555556</v>
-      </c>
-      <c r="J15" s="4">
-        <v>55.82222222222222</v>
-      </c>
-    </row>
-    <row r="18">
+        <v>35.755000000000003</v>
+      </c>
+      <c r="I15" s="1">
+        <v>68.47</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D18" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E18" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F18" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
         <v>24</v>
@@ -818,11 +761,8 @@
       <c r="I18" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19">
+    </row>
+    <row r="19" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -830,25 +770,22 @@
         <v>15</v>
       </c>
       <c r="E19" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F19" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G19" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H19" s="1">
-        <v>312.641</v>
-      </c>
-      <c r="I19" s="4">
-        <v>249.66422222222218</v>
-      </c>
-      <c r="J19" s="4">
-        <v>75.6</v>
-      </c>
-    </row>
-    <row r="20">
+        <v>316.447</v>
+      </c>
+      <c r="I19" s="1">
+        <v>249.81</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>16</v>
       </c>
@@ -856,25 +793,22 @@
         <v>17</v>
       </c>
       <c r="E20" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F20" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G20" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H20" s="1">
-        <v>96.346</v>
-      </c>
-      <c r="I20" s="4">
-        <v>155.64311111111118</v>
-      </c>
-      <c r="J20" s="4">
-        <v>66.31111111111112</v>
-      </c>
-    </row>
-    <row r="21">
+        <v>97.531000000000006</v>
+      </c>
+      <c r="I20" s="1">
+        <v>172.77</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>18</v>
       </c>
@@ -882,25 +816,22 @@
         <v>19</v>
       </c>
       <c r="E21" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F21" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G21" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H21" s="1">
-        <v>47.15</v>
-      </c>
-      <c r="I21" s="4">
-        <v>75.08177777777777</v>
-      </c>
-      <c r="J21" s="4">
-        <v>56.2</v>
-      </c>
-    </row>
-    <row r="22">
+        <v>47.588000000000001</v>
+      </c>
+      <c r="I21" s="1">
+        <v>90.66</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>20</v>
       </c>
@@ -908,25 +839,22 @@
         <v>21</v>
       </c>
       <c r="E22" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F22" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G22" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H22" s="1">
-        <v>37.849</v>
-      </c>
-      <c r="I22" s="4">
-        <v>61.957777777777764</v>
-      </c>
-      <c r="J22" s="4">
-        <v>54.733333333333334</v>
-      </c>
-    </row>
-    <row r="23">
+        <v>38.243000000000002</v>
+      </c>
+      <c r="I22" s="1">
+        <v>77.88</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>22</v>
       </c>
@@ -934,51 +862,45 @@
         <v>23</v>
       </c>
       <c r="E23" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F23" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="G23" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H23" s="1">
-        <v>40.67</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="J23" s="7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27">
+        <v>40.953000000000003</v>
+      </c>
+      <c r="I23" s="4">
+        <v>82.14</v>
+      </c>
+    </row>
+    <row r="27" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D27" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E27" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F27" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G27" s="1">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="H27" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="J27" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="28">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>14</v>
       </c>
@@ -986,25 +908,22 @@
         <v>15</v>
       </c>
       <c r="E28" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F28" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G28" s="1">
-        <v>32.0</v>
+        <v>32</v>
       </c>
       <c r="H28" s="1">
-        <v>667.557</v>
-      </c>
-      <c r="I28" s="4">
-        <v>228.76000000000005</v>
-      </c>
-      <c r="J28" s="4">
-        <v>70.53333333333333</v>
-      </c>
-    </row>
-    <row r="29">
+        <v>667.548</v>
+      </c>
+      <c r="I28" s="1">
+        <v>241.1</v>
+      </c>
+    </row>
+    <row r="29" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>16</v>
       </c>
@@ -1012,25 +931,22 @@
         <v>17</v>
       </c>
       <c r="E29" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F29" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G29" s="1">
-        <v>128.0</v>
+        <v>128</v>
       </c>
       <c r="H29" s="1">
-        <v>114.959</v>
+        <v>115.756</v>
       </c>
       <c r="I29" s="1">
-        <v>184.86377777777773</v>
-      </c>
-      <c r="J29" s="1">
-        <v>65.53333333333333</v>
-      </c>
-    </row>
-    <row r="30">
+        <v>192.78</v>
+      </c>
+    </row>
+    <row r="30" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>18</v>
       </c>
@@ -1038,25 +954,22 @@
         <v>19</v>
       </c>
       <c r="E30" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F30" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G30" s="1">
-        <v>512.0</v>
+        <v>512</v>
       </c>
       <c r="H30" s="1">
-        <v>36.083</v>
+        <v>36.518999999999998</v>
       </c>
       <c r="I30" s="1">
-        <v>66.44577777777778</v>
-      </c>
-      <c r="J30" s="1">
-        <v>48.666666666666664</v>
-      </c>
-    </row>
-    <row r="31">
+        <v>81.209999999999994</v>
+      </c>
+    </row>
+    <row r="31" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>20</v>
       </c>
@@ -1064,25 +977,22 @@
         <v>21</v>
       </c>
       <c r="E31" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F31" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G31" s="1">
-        <v>2048.0</v>
+        <v>2048</v>
       </c>
       <c r="H31" s="1">
-        <v>25.786</v>
-      </c>
-      <c r="I31" s="4">
-        <v>41.82799999999998</v>
-      </c>
-      <c r="J31" s="4">
-        <v>44.55555555555556</v>
-      </c>
-    </row>
-    <row r="32">
+        <v>26.105</v>
+      </c>
+      <c r="I31" s="1">
+        <v>59.98</v>
+      </c>
+    </row>
+    <row r="32" spans="3:9" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>22</v>
       </c>
@@ -1090,89 +1000,60 @@
         <v>23</v>
       </c>
       <c r="E32" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F32" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G32" s="1">
-        <v>8192.0</v>
+        <v>8192</v>
       </c>
       <c r="H32" s="1">
-        <v>25.888</v>
-      </c>
-      <c r="I32" s="4">
-        <v>52.52599999999999</v>
-      </c>
-      <c r="J32" s="4">
-        <v>43.48888888888889</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B37" s="8" t="s">
+        <v>26.055</v>
+      </c>
+      <c r="I32" s="1">
+        <v>53.25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="8" t="s">
-        <v>30</v>
-      </c>
-      <c r="F37" s="8" t="s">
-        <v>31</v>
-      </c>
-      <c r="G37" s="8" t="s">
-        <v>32</v>
-      </c>
-      <c r="H37" s="8" t="s">
-        <v>33</v>
-      </c>
-      <c r="I37" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>36</v>
-      </c>
       <c r="C38" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D38" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D38" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E38" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F38" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G38" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H38" s="1">
-        <v>8.08317</v>
+        <v>8.0831700000000009</v>
       </c>
       <c r="I38" s="1">
         <v>21.39</v>
       </c>
-      <c r="J38" s="1">
-        <v>34.0</v>
-      </c>
-    </row>
-    <row r="39">
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,25 +1061,22 @@
         <v>15</v>
       </c>
       <c r="E39" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F39" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G39" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H39" s="1">
-        <v>2.03883</v>
-      </c>
-      <c r="I39" s="4">
+        <v>2.0388299999999999</v>
+      </c>
+      <c r="I39" s="1">
         <v>24.510489977728156</v>
       </c>
-      <c r="J39" s="4">
-        <v>34.051224944320715</v>
-      </c>
-    </row>
-    <row r="40">
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>16</v>
       </c>
@@ -1206,25 +1084,22 @@
         <v>17</v>
       </c>
       <c r="E40" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F40" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G40" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H40" s="1">
-        <v>0.52762</v>
-      </c>
-      <c r="I40" s="4">
-        <v>23.25728285077954</v>
-      </c>
-      <c r="J40" s="4">
-        <v>34.075723830734965</v>
-      </c>
-    </row>
-    <row r="41">
+        <v>0.52761999999999998</v>
+      </c>
+      <c r="I40" s="1">
+        <v>23.257282850779539</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>18</v>
       </c>
@@ -1232,25 +1107,22 @@
         <v>19</v>
       </c>
       <c r="E41" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F41" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G41" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H41" s="1">
-        <v>0.27364</v>
-      </c>
-      <c r="I41" s="4">
+        <v>0.27363999999999999</v>
+      </c>
+      <c r="I41" s="1">
         <v>22.577104677060124</v>
       </c>
-      <c r="J41" s="4">
-        <v>34.055679287305125</v>
-      </c>
-    </row>
-    <row r="42">
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>20</v>
       </c>
@@ -1258,80 +1130,71 @@
         <v>21</v>
       </c>
       <c r="E42" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F42" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H42" s="1">
-        <v>0.27999</v>
-      </c>
-      <c r="I42" s="4">
+        <v>0.27999000000000002</v>
+      </c>
+      <c r="I42" s="1">
         <v>22.221648106904244</v>
       </c>
-      <c r="J42" s="4">
-        <v>34.10913140311804</v>
-      </c>
-    </row>
-    <row r="43">
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E43" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F43" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G43" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H43" s="1">
-        <v>0.2696</v>
-      </c>
-      <c r="I43" s="4">
-        <v>21.9708240534521</v>
-      </c>
-      <c r="J43" s="4">
-        <v>34.211581291759465</v>
-      </c>
-    </row>
-    <row r="47">
+        <v>0.26960000000000001</v>
+      </c>
+      <c r="I43" s="1">
+        <v>21.970824053452102</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B47" s="1" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C47" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D47" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D47" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E47" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F47" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G47" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H47" s="1">
-        <v>8.09121</v>
-      </c>
-      <c r="I47" s="4">
+        <v>8.0912100000000002</v>
+      </c>
+      <c r="I47" s="1">
         <v>21.05345211581291</v>
       </c>
-      <c r="J47" s="4">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="48">
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>14</v>
       </c>
@@ -1339,25 +1202,22 @@
         <v>15</v>
       </c>
       <c r="E48" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F48" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G48" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H48" s="1">
-        <v>2.04756</v>
-      </c>
-      <c r="I48" s="4">
+        <v>2.0475599999999998</v>
+      </c>
+      <c r="I48" s="1">
         <v>22.236013363028988</v>
       </c>
-      <c r="J48" s="4">
-        <v>35.01336302895323</v>
-      </c>
-    </row>
-    <row r="49">
+    </row>
+    <row r="49" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>16</v>
       </c>
@@ -1365,25 +1225,22 @@
         <v>17</v>
       </c>
       <c r="E49" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F49" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G49" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>0.52767</v>
-      </c>
-      <c r="I49" s="4">
+        <v>0.52766999999999997</v>
+      </c>
+      <c r="I49" s="1">
         <v>21.486971046770602</v>
       </c>
-      <c r="J49" s="4">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="50">
+    </row>
+    <row r="50" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>18</v>
       </c>
@@ -1391,25 +1248,22 @@
         <v>19</v>
       </c>
       <c r="E50" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F50" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G50" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H50" s="1">
-        <v>0.27134</v>
-      </c>
-      <c r="I50" s="4">
+        <v>0.27134000000000003</v>
+      </c>
+      <c r="I50" s="1">
         <v>22.011625835189335</v>
       </c>
-      <c r="J50" s="4">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="51">
+    </row>
+    <row r="51" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>20</v>
       </c>
@@ -1417,80 +1271,71 @@
         <v>21</v>
       </c>
       <c r="E51" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F51" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G51" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H51" s="1">
-        <v>0.28039</v>
-      </c>
-      <c r="I51" s="4">
+        <v>0.28038999999999997</v>
+      </c>
+      <c r="I51" s="1">
         <v>22.364298440979912</v>
       </c>
-      <c r="J51" s="4">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="52">
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E52" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F52" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G52" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="H52" s="1">
-        <v>0.26416</v>
-      </c>
-      <c r="I52" s="4">
+        <v>0.26416000000000001</v>
+      </c>
+      <c r="I52" s="1">
         <v>22.596124721603545</v>
       </c>
-      <c r="J52" s="4">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="59">
+    </row>
+    <row r="59" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B59" s="1" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D59" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D59" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E59" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F59" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G59" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H59" s="1">
-        <v>8.07801</v>
-      </c>
-      <c r="I59" s="4">
+        <v>8.0780100000000008</v>
+      </c>
+      <c r="I59" s="1">
         <v>21.456213808463218</v>
       </c>
-      <c r="J59" s="4">
-        <v>35.00890868596882</v>
-      </c>
-    </row>
-    <row r="60">
+    </row>
+    <row r="60" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>14</v>
       </c>
@@ -1498,25 +1343,22 @@
         <v>15</v>
       </c>
       <c r="E60" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F60" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G60" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H60" s="1">
-        <v>2.05255</v>
-      </c>
-      <c r="I60" s="4">
-        <v>22.81461024498885</v>
-      </c>
-      <c r="J60" s="4">
-        <v>35.03563474387528</v>
-      </c>
-    </row>
-    <row r="61">
+        <v>2.0525500000000001</v>
+      </c>
+      <c r="I60" s="1">
+        <v>22.814610244988849</v>
+      </c>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>16</v>
       </c>
@@ -1524,25 +1366,22 @@
         <v>17</v>
       </c>
       <c r="E61" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F61" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G61" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H61" s="1">
-        <v>0.52895</v>
-      </c>
-      <c r="I61" s="4">
+        <v>0.52895000000000003</v>
+      </c>
+      <c r="I61" s="1">
         <v>21.363763919821718</v>
       </c>
-      <c r="J61" s="4">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="62">
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>18</v>
       </c>
@@ -1550,25 +1389,22 @@
         <v>19</v>
       </c>
       <c r="E62" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F62" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G62" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H62" s="1">
-        <v>0.26446</v>
-      </c>
-      <c r="I62" s="4">
+        <v>0.26445999999999997</v>
+      </c>
+      <c r="I62" s="1">
         <v>21.599109131403093</v>
       </c>
-      <c r="J62" s="4">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="63">
+    </row>
+    <row r="63" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>20</v>
       </c>
@@ -1576,74 +1412,71 @@
         <v>21</v>
       </c>
       <c r="E63" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F63" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G63" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H63" s="1">
         <v>0.26055</v>
       </c>
-      <c r="I63" s="4">
-        <v>22.67973273942095</v>
-      </c>
-      <c r="J63" s="4">
-        <v>35.02672605790646</v>
-      </c>
-    </row>
-    <row r="64">
+      <c r="I63" s="1">
+        <v>22.679732739420949</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D64" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E64" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F64" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G64" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H64" s="1">
-        <v>0.51442</v>
-      </c>
-      <c r="I64" s="4">
+        <v>0.51441999999999999</v>
+      </c>
+      <c r="I64" s="1">
         <v>22.066057906458774</v>
       </c>
-      <c r="J64" s="4">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="69">
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B69" s="1" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="C69" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D69" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D69" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E69" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F69" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G69" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H69" s="1">
-        <v>8.05763</v>
-      </c>
-    </row>
-    <row r="70">
+        <v>8.0576299999999996</v>
+      </c>
+      <c r="I69" s="1">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="70" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>14</v>
       </c>
@@ -1651,19 +1484,22 @@
         <v>15</v>
       </c>
       <c r="E70" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F70" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G70" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H70" s="1">
         <v>2.05247</v>
       </c>
-    </row>
-    <row r="71">
+      <c r="I70" s="1">
+        <v>20.88</v>
+      </c>
+    </row>
+    <row r="71" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>16</v>
       </c>
@@ -1671,19 +1507,22 @@
         <v>17</v>
       </c>
       <c r="E71" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F71" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G71" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H71" s="1">
         <v>0.52964</v>
       </c>
-    </row>
-    <row r="72">
+      <c r="I71" s="1">
+        <v>20.97</v>
+      </c>
+    </row>
+    <row r="72" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>18</v>
       </c>
@@ -1691,19 +1530,22 @@
         <v>19</v>
       </c>
       <c r="E72" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F72" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G72" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H72" s="1">
-        <v>0.26728</v>
-      </c>
-    </row>
-    <row r="73">
+        <v>0.26728000000000002</v>
+      </c>
+      <c r="I72" s="1">
+        <v>20.77</v>
+      </c>
+    </row>
+    <row r="73" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>20</v>
       </c>
@@ -1711,68 +1553,71 @@
         <v>21</v>
       </c>
       <c r="E73" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F73" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G73" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="1">
-        <v>0.26952</v>
-      </c>
-    </row>
-    <row r="74">
+        <v>0.26951999999999998</v>
+      </c>
+      <c r="I73" s="1">
+        <v>21.29</v>
+      </c>
+    </row>
+    <row r="74" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D74" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E74" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F74" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G74" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H74" s="1">
-        <v>0.27116</v>
-      </c>
-    </row>
-    <row r="78">
+        <v>0.27116000000000001</v>
+      </c>
+      <c r="I74" s="1">
+        <v>21.22</v>
+      </c>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B78" s="1" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="C78" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D78" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D78" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E78" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F78" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G78" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H78" s="1">
-        <v>8.0364</v>
-      </c>
-      <c r="I78" s="4">
-        <v>20.91654788418711</v>
-      </c>
-      <c r="J78" s="4">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="79">
+        <v>8.0364000000000004</v>
+      </c>
+      <c r="I78" s="1">
+        <v>20.916547884187111</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C79" s="1" t="s">
         <v>14</v>
       </c>
@@ -1780,25 +1625,22 @@
         <v>15</v>
       </c>
       <c r="E79" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F79" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G79" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H79" s="1">
-        <v>2.10458</v>
-      </c>
-      <c r="I79" s="4">
-        <v>20.68532293986638</v>
-      </c>
-      <c r="J79" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="80">
+        <v>2.1045799999999999</v>
+      </c>
+      <c r="I79" s="1">
+        <v>20.685322939866381</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>16</v>
       </c>
@@ -1806,25 +1648,22 @@
         <v>17</v>
       </c>
       <c r="E80" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F80" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G80" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H80" s="1">
         <v>0.52964</v>
       </c>
-      <c r="I80" s="4">
+      <c r="I80" s="1">
         <v>20.930000000000035</v>
       </c>
-      <c r="J80" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="81">
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>18</v>
       </c>
@@ -1832,25 +1671,22 @@
         <v>19</v>
       </c>
       <c r="E81" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F81" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G81" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H81" s="1">
-        <v>0.26736</v>
-      </c>
-      <c r="I81" s="4">
+        <v>0.26735999999999999</v>
+      </c>
+      <c r="I81" s="1">
         <v>21.072538975501125</v>
       </c>
-      <c r="J81" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="82">
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>20</v>
       </c>
@@ -1858,80 +1694,71 @@
         <v>21</v>
       </c>
       <c r="E82" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F82" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G82" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H82" s="1">
-        <v>0.26933</v>
-      </c>
-      <c r="I82" s="4">
+        <v>0.26933000000000001</v>
+      </c>
+      <c r="I82" s="1">
         <v>21.267305122494424</v>
       </c>
-      <c r="J82" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="83">
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D83" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E83" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F83" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G83" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H83" s="1">
-        <v>0.26436</v>
-      </c>
-      <c r="I83" s="4">
-        <v>21.28015590200443</v>
-      </c>
-      <c r="J83" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="88">
+        <v>0.26435999999999998</v>
+      </c>
+      <c r="I83" s="1">
+        <v>21.280155902004431</v>
+      </c>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B88" s="1" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="C88" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D88" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E88" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F88" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G88" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H88" s="1">
-        <v>8.0872</v>
-      </c>
-      <c r="I88" s="4">
+        <v>8.0871999999999993</v>
+      </c>
+      <c r="I88" s="1">
         <v>21.242271714922005</v>
       </c>
-      <c r="J88" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="89">
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>14</v>
       </c>
@@ -1939,25 +1766,22 @@
         <v>15</v>
       </c>
       <c r="E89" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F89" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G89" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H89" s="1">
-        <v>2.10454</v>
-      </c>
-      <c r="I89" s="4">
-        <v>21.2898663697105</v>
-      </c>
-      <c r="J89" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="90">
+        <v>2.1045400000000001</v>
+      </c>
+      <c r="I89" s="1">
+        <v>21.289866369710499</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>16</v>
       </c>
@@ -1965,25 +1789,22 @@
         <v>17</v>
       </c>
       <c r="E90" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F90" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G90" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H90" s="1">
-        <v>0.52961</v>
-      </c>
-      <c r="I90" s="4">
+        <v>0.52961000000000003</v>
+      </c>
+      <c r="I90" s="1">
         <v>21.515167037861897</v>
       </c>
-      <c r="J90" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="91">
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>18</v>
       </c>
@@ -1991,25 +1812,22 @@
         <v>19</v>
       </c>
       <c r="E91" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F91" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G91" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H91" s="1">
-        <v>0.26792</v>
-      </c>
-      <c r="I91" s="4">
+        <v>0.26791999999999999</v>
+      </c>
+      <c r="I91" s="1">
         <v>21.214855233852994</v>
       </c>
-      <c r="J91" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="92">
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>20</v>
       </c>
@@ -2017,83 +1835,71 @@
         <v>21</v>
       </c>
       <c r="E92" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F92" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G92" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H92" s="1">
-        <v>0.26925</v>
-      </c>
-      <c r="I92" s="4">
+        <v>0.26924999999999999</v>
+      </c>
+      <c r="I92" s="1">
         <v>20.827327394209284</v>
       </c>
-      <c r="J92" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="93">
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D93" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E93" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F93" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G93" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H93" s="1">
-        <v>0.26429</v>
+        <v>0.26429000000000002</v>
       </c>
       <c r="I93" s="1">
         <v>21.05801781737193</v>
       </c>
-      <c r="J93" s="1">
-        <v>34.0</v>
-      </c>
-    </row>
-    <row r="97">
+    </row>
+    <row r="97" spans="2:9" x14ac:dyDescent="0.2">
       <c r="H97" s="1"/>
     </row>
-    <row r="98">
+    <row r="98" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B98" s="1" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C98" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D98" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D98" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E98" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F98" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G98" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H98" s="1">
-        <v>8.04756</v>
-      </c>
-      <c r="I98" s="4">
-        <v>21.18739420935417</v>
-      </c>
-      <c r="J98" s="1">
-        <v>34.0</v>
-      </c>
-    </row>
-    <row r="99">
+        <v>8.0475600000000007</v>
+      </c>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>14</v>
       </c>
@@ -2101,25 +1907,22 @@
         <v>15</v>
       </c>
       <c r="E99" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F99" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G99" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H99" s="1">
-        <v>2.05909</v>
-      </c>
-      <c r="I99" s="4">
-        <v>24.31409799554564</v>
-      </c>
-      <c r="J99" s="4">
-        <v>34.25389755011136</v>
-      </c>
-    </row>
-    <row r="100">
+        <v>2.0590899999999999</v>
+      </c>
+      <c r="I99" s="1">
+        <v>21.187394209354171</v>
+      </c>
+    </row>
+    <row r="100" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>16</v>
       </c>
@@ -2127,25 +1930,22 @@
         <v>17</v>
       </c>
       <c r="E100" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F100" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G100" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H100" s="1">
         <v>0.52764</v>
       </c>
-      <c r="I100" s="4">
-        <v>21.490311804008908</v>
-      </c>
-      <c r="J100" s="4">
-        <v>34.99331848552338</v>
-      </c>
-    </row>
-    <row r="101">
+      <c r="I100" s="1">
+        <v>24.314097995545641</v>
+      </c>
+    </row>
+    <row r="101" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>18</v>
       </c>
@@ -2153,25 +1953,22 @@
         <v>19</v>
       </c>
       <c r="E101" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F101" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G101" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H101" s="1">
-        <v>0.27219</v>
-      </c>
-      <c r="I101" s="4">
-        <v>21.45080178173715</v>
-      </c>
-      <c r="J101" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="102">
+        <v>0.27218999999999999</v>
+      </c>
+      <c r="I101" s="1">
+        <v>21.490311804008908</v>
+      </c>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>20</v>
       </c>
@@ -2179,74 +1976,71 @@
         <v>21</v>
       </c>
       <c r="E102" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F102" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G102" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H102" s="1">
         <v>0.28086</v>
       </c>
-      <c r="I102" s="4">
-        <v>21.375812917594654</v>
-      </c>
-      <c r="J102" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="103">
+      <c r="I102" s="1">
+        <v>21.450801781737152</v>
+      </c>
+    </row>
+    <row r="103" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C103" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D103" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E103" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F103" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G103" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H103" s="1">
-        <v>0.26503</v>
-      </c>
-    </row>
-    <row r="107">
+        <v>0.26502999999999999</v>
+      </c>
+      <c r="I103" s="1">
+        <v>21.375812917594654</v>
+      </c>
+    </row>
+    <row r="107" spans="2:9" x14ac:dyDescent="0.2">
       <c r="B107" s="1" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C107" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D107" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D107" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E107" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F107" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G107" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H107" s="1">
-        <v>8.08509</v>
-      </c>
-      <c r="I107" s="4">
+        <v>8.0850899999999992</v>
+      </c>
+      <c r="I107" s="1">
         <v>22.119443207126878</v>
       </c>
-      <c r="J107" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="108">
+    </row>
+    <row r="108" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C108" s="1" t="s">
         <v>14</v>
       </c>
@@ -2254,25 +2048,22 @@
         <v>15</v>
       </c>
       <c r="E108" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F108" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G108" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H108" s="1">
-        <v>2.10448</v>
-      </c>
-      <c r="I108" s="4">
+        <v>2.1044800000000001</v>
+      </c>
+      <c r="I108" s="1">
         <v>21.413073496659244</v>
       </c>
-      <c r="J108" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="109">
+    </row>
+    <row r="109" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C109" s="1" t="s">
         <v>16</v>
       </c>
@@ -2280,25 +2071,22 @@
         <v>17</v>
       </c>
       <c r="E109" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F109" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G109" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H109" s="1">
-        <v>0.5889</v>
-      </c>
-      <c r="I109" s="4">
+        <v>0.58889999999999998</v>
+      </c>
+      <c r="I109" s="1">
         <v>21.530022271714902</v>
       </c>
-      <c r="J109" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="110">
+    </row>
+    <row r="110" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C110" s="1" t="s">
         <v>18</v>
       </c>
@@ -2306,25 +2094,22 @@
         <v>19</v>
       </c>
       <c r="E110" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F110" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G110" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H110" s="1">
         <v>0.44599</v>
       </c>
-      <c r="I110" s="4">
-        <v>21.45358574610251</v>
-      </c>
-      <c r="J110" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="111">
+      <c r="I110" s="1">
+        <v>21.453585746102512</v>
+      </c>
+    </row>
+    <row r="111" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C111" s="1" t="s">
         <v>20</v>
       </c>
@@ -2332,39 +2117,36 @@
         <v>21</v>
       </c>
       <c r="E111" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F111" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G111" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H111" s="1">
-        <v>0.35204</v>
-      </c>
-      <c r="I111" s="4">
+        <v>0.35204000000000002</v>
+      </c>
+      <c r="I111" s="1">
         <v>20.975434298440973</v>
       </c>
-      <c r="J111" s="1">
-        <v>35.0</v>
-      </c>
-    </row>
-    <row r="112">
+    </row>
+    <row r="112" spans="2:9" x14ac:dyDescent="0.2">
       <c r="C112" s="1" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="D112" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E112" s="1">
-        <v>1.6777216E7</v>
+        <v>16777216</v>
       </c>
       <c r="F112" s="1">
-        <v>0.0</v>
+        <v>0</v>
       </c>
       <c r="G112" s="1">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="H112" s="1">
         <v>0.27509</v>
@@ -2372,30 +2154,27 @@
       <c r="I112" s="1">
         <v>20.774955357142854</v>
       </c>
-      <c r="J112" s="1">
-        <v>35.0</v>
-      </c>
     </row>
   </sheetData>
-  <printOptions gridLines="1" horizontalCentered="1"/>
-  <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup fitToHeight="0" cellComments="atEnd" orientation="landscape" pageOrder="overThenDown"/>
-  <drawing r:id="rId1"/>
+  <printOptions horizontalCentered="1" gridLines="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
+  <pageSetup fitToHeight="0" pageOrder="overThenDown" orientation="landscape" cellComments="atEnd"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   <sheetData/>
   <conditionalFormatting sqref="A1">
     <cfRule type="notContainsBlanks" dxfId="0" priority="1">
       <formula>LEN(TRIM(A1))&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>